--- a/AAVA_Files/Centene_Healthcare_Test_Scenarios.xlsx
+++ b/AAVA_Files/Centene_Healthcare_Test_Scenarios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Validate Member Enrollment Demographics</t>
+          <t>Validate Member Demographics During Enrollment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,17 +513,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1. Enter new member details;2. Submit enrollment;3. System validates demographics</t>
+          <t>1. Navigate to enrollment form;2. Enter member demographic details;3. Submit for validation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Demographic details are validated successfully; No errors displayed</t>
+          <t>System validates details and returns success if valid, else shows error</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enrollment record created</t>
+          <t>Member is either enrolled or notified of error</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Member Enrollment</t>
+          <t>Enrollment Management</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Demographics Validation</t>
+          <t>Demographic Validation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Covers positive path</t>
+          <t>Covers positive and negative validation</t>
         </is>
       </c>
     </row>
@@ -570,27 +570,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Detect Duplicate Member Records</t>
+          <t>Duplicate Member Record Detection</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>User is logged into enrollment system; Existing member data present</t>
+          <t>User is on enrollment submission page</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1. Enter duplicate member details;2. Submit enrollment</t>
+          <t>1. Enter member details matching an existing record;2. Submit enrollment</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>System flags duplicate record; Error message displayed</t>
+          <t>System flags duplicate and prevents submission</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No duplicate record created</t>
+          <t>No duplicate member created</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Member Enrollment</t>
+          <t>Enrollment Management</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Duplicate Check</t>
+          <t>Duplicate Detection</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Negative scenario</t>
+          <t>Edge case: similar names, different DOB</t>
         </is>
       </c>
     </row>
@@ -637,27 +637,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Generate Enrollment Confirmation</t>
+          <t>Enrollment Confirmation Generation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User is logged into enrollment system; Valid member details entered</t>
+          <t>Successful member enrollment</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1. Complete enrollment submission</t>
+          <t>1. Complete enrollment process;2. Submit details</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enrollment confirmation generated and displayed</t>
+          <t>System generates and displays confirmation</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Confirmation sent to member</t>
+          <t>Confirmation is stored and accessible</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Member Enrollment</t>
+          <t>Enrollment Management</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Confirmation</t>
+          <t>Confirmation Generation</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Covers confirmation flow</t>
+          <t>Check for confirmation format</t>
         </is>
       </c>
     </row>
@@ -704,27 +704,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Claims Validation Against Eligibility</t>
+          <t>Claims Validation Against Member Eligibility</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Claims system access; Valid member and claim data</t>
+          <t>User is logged into claims system; Member exists</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1. Submit claim for processing</t>
+          <t>1. Submit claim for a member;2. System checks eligibility</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Claim validated against member eligibility</t>
+          <t>Claim is validated or denied based on eligibility</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Claim proceeds to adjudication</t>
+          <t>Claim status updated</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Positive path</t>
+          <t>Negative: Ineligible member</t>
         </is>
       </c>
     </row>
@@ -771,27 +771,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apply Policy Rules and Benefit Limits</t>
+          <t>Policy Rules and Benefit Limits Application</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Claims system access; Valid claim submitted</t>
+          <t>Claim is ready for adjudication</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1. Process claim;2. Apply policy rules</t>
+          <t>1. Submit claim;2. System applies policy rules;3. System checks benefit limits</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Policy rules and limits applied; Only eligible amounts approved</t>
+          <t>Claim is adjudicated per rules; limits enforced</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Claim status updated</t>
+          <t>Claim processed or denied</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Boundary scenario</t>
+          <t>Boundary: Max benefit limit</t>
         </is>
       </c>
     </row>
@@ -843,22 +843,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Claims system access; Claim not meeting criteria</t>
+          <t>Claim is denied</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1. Submit ineligible claim</t>
+          <t>1. Submit claim with invalid details;2. System denies claim</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Claim denied; EOB generated and sent</t>
+          <t>EOB is generated with denial reason</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Provider receives EOB</t>
+          <t>EOB accessible to provider</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Denial Handling</t>
+          <t>EOB Generation</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Negative scenario</t>
+          <t>Check EOB content</t>
         </is>
       </c>
     </row>
@@ -905,27 +905,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Provider License Validation</t>
+          <t>Provider License Validation During Credential Update</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provider admin access; Provider record to update</t>
+          <t>Provider is updating credentials</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1. Edit provider info;2. Submit update</t>
+          <t>1. Edit provider profile;2. Enter license details;3. Submit update</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>System validates provider license; Rejects invalid license</t>
+          <t>System validates license and accepts/rejects update</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Provider record updated if valid</t>
+          <t>Provider record updated or rejected</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Provider Network</t>
+          <t>Provider Management</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Security scenario</t>
+          <t>Negative: Expired license</t>
         </is>
       </c>
     </row>
@@ -977,22 +977,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provider admin access</t>
+          <t>Provider change is submitted</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1. Update provider details</t>
+          <t>1. Update provider information;2. Submit changes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>All changes are audited and logged</t>
+          <t>System logs and audits all changes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Audit log updated</t>
+          <t>Audit log entry created</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Provider Network</t>
+          <t>Provider Management</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Compliance requirement</t>
+          <t>Check log for accuracy</t>
         </is>
       </c>
     </row>
@@ -1039,27 +1039,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Update Reflected in Member Portal</t>
+          <t>Provider Info Update Reflected in Portal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Provider info updated; Member portal integration</t>
+          <t>Provider update is approved</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1. Update provider details;2. Check member portal after 24h</t>
+          <t>1. Complete provider update;2. Wait for sync</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Updated info appears in portal within 24 hours</t>
+          <t>Member portal shows updated provider info within 24 hours</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Members see current data</t>
+          <t>Portal data matches backend</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Provider Network</t>
+          <t>Provider Management</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Time-bound scenario</t>
+          <t>Check for sync delay</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Clinical Documentation for Prior Auth</t>
+          <t>Clinical Documentation Required for Prior Auth</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nurse access; Prior auth request submitted</t>
+          <t>Nurse is reviewing prior auth request</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1. Submit prior auth request without documentation</t>
+          <t>1. Open prior auth request;2. Check for attached clinical docs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>System rejects request; Error for missing documentation</t>
+          <t>System rejects requests without documentation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No request created</t>
+          <t>Request status is updated</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Prior Authorization</t>
+          <t>Prior Auth Workflow</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Documentation Check</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Negative scenario</t>
+          <t>Negative: Missing docs</t>
         </is>
       </c>
     </row>
@@ -1173,27 +1173,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Route Cases by Service Type</t>
+          <t>Case Routing Based on Service Type</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nurse access; Prior auth request with documentation</t>
+          <t>Prior auth request is submitted</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1. Submit request for different service types</t>
+          <t>1. Submit request with service type;2. System routes case</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cases routed to appropriate queue</t>
+          <t>Case is routed to appropriate queue</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Request assigned correctly</t>
+          <t>Queue assignment visible</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Prior Authorization</t>
+          <t>Prior Auth Workflow</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Routing</t>
+          <t>Case Routing</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Routing logic</t>
+          <t>Boundary: Unknown type</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Decision Notification for Prior Auth</t>
+          <t>Decision Notifications Sent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nurse access; Request approved/denied</t>
+          <t>Prior auth decision made</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1. Approve or deny request</t>
+          <t>1. Approve/deny request;2. System sends notifications</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Notification sent to provider and member</t>
+          <t>Providers and members receive notifications</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Prior Authorization</t>
+          <t>Prior Auth Workflow</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Covers both outcomes</t>
+          <t>Check notification content</t>
         </is>
       </c>
     </row>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Secure Member Portal Login</t>
+          <t>Secure Login with MFA for Member Portal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Member portal access enabled</t>
+          <t>Member has portal account</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1. Navigate to login;2. Enter credentials;3. Complete MFA</t>
+          <t>1. Open portal login;2. Enter credentials;3. Complete MFA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Login successful with MFA</t>
+          <t>System authenticates user securely</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Session established securely</t>
+          <t>User gains access</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Security scenario</t>
+          <t>Negative: Wrong MFA code</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Member has claims; Portal access</t>
+          <t>Member is logged into portal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1. Log in;2. View claims status</t>
+          <t>1. Navigate to claims section</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Claims status displayed in real time</t>
+          <t>Claims status shown in real-time</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Member sees up-to-date info</t>
+          <t>Status matches backend</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Positive path</t>
+          <t>Check for delays</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1446,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Member logged in; ID card available</t>
+          <t>Member is logged into portal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1. Navigate to ID card;2. Download digital card</t>
+          <t>1. Navigate to ID card section;2. Click download</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Digital ID card downloaded successfully</t>
+          <t>Digital ID card downloads successfully</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>File saved to device</t>
+          <t>File is accessible to member</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Usability scenario</t>
+          <t>Check file format</t>
         </is>
       </c>
     </row>
@@ -1508,27 +1508,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Generate CMS-Compliant Reports</t>
+          <t>Regulatory Report Generation per CMS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Compliance officer access; Reporting module enabled</t>
+          <t>User is compliance officer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1. Select CMS report;2. Generate report</t>
+          <t>1. Open reporting module;2. Select CMS report;3. Generate report</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Report aligns with CMS guidelines</t>
+          <t>Report matches CMS format</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Report archived</t>
+          <t>Report is stored and accessible</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Reporting &amp; Compliance</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CMS Compliance</t>
+          <t>CMS Reporting</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Regulatory requirement</t>
+          <t>Check for compliance updates</t>
         </is>
       </c>
     </row>
@@ -1575,27 +1575,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Extract Data from Validated Sources</t>
+          <t>Data Extraction from Validated Sources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Reporting module enabled; Validated data sources</t>
+          <t>Reporting job is scheduled</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1. Generate regulatory report</t>
+          <t>1. Configure data sources;2. Run report job</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data sourced only from validated sources</t>
+          <t>Data extracted only from validated sources</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Report generated with integrity</t>
+          <t>Report accuracy ensured</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Reporting &amp; Compliance</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Data Integrity</t>
+          <t>Data Extraction</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Negative: Invalid data source</t>
         </is>
       </c>
     </row>
@@ -1642,27 +1642,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Maintain Audit Logs for Reports</t>
+          <t>Audit Logs for Report Generation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Reporting module enabled</t>
+          <t>Report is generated</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1. Generate report;2. Review audit log</t>
+          <t>1. Generate regulatory report</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Audit log entry created for each report</t>
+          <t>Audit log entry created for report generation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Audit trail complete</t>
+          <t>Logs are reviewable</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Reporting &amp; Compliance</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1697,141 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Compliance requirement</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TS-019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Boundary Test: Max Length Fields</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>System access; Field with max length constraint</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1. Enter max allowed characters;2. Submit</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Submission accepted without error</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Record saved</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Centene_Healthcare</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>All Modules</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Boundary</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>SIMULATED</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Boundary scenario</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TS-020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Negative Test: Invalid Data Entry</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>System access</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1. Enter invalid data (e.g., special chars, blank fields);2. Submit</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>System displays validation errors</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>No record created</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Centene_Healthcare</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>All Modules</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>SIMULATED</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Data validation</t>
+          <t>Check for missing logs</t>
         </is>
       </c>
     </row>

--- a/AAVA_Files/Centene_Healthcare_Test_Scenarios.xlsx
+++ b/AAVA_Files/Centene_Healthcare_Test_Scenarios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,32 +503,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Validate Member Demographics During Enrollment</t>
+          <t>Capture and Validate New Member Enrollment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>User is logged into enrollment system; Access to state eligibility systems</t>
+          <t>User logged in as Member Services Rep; Access to enrollment module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1. Navigate to enrollment form;2. Enter member demographic details;3. Submit for validation</t>
+          <t>1. Navigate to Member Enrollment;2. Enter valid demographic details;3. Submit enrollment</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>System validates details and returns success if valid, else shows error</t>
+          <t>Enrollment submitted successfully; Confirmation generated</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Member is either enrolled or notified of error</t>
+          <t>Member record created; Confirmation available</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Enrollment Management</t>
+          <t>Member Enrollment</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Demographic Validation</t>
+          <t>Enrollment Validation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Covers positive and negative validation</t>
+          <t>Covers basic enrollment success</t>
         </is>
       </c>
     </row>
@@ -570,32 +570,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Duplicate Member Record Detection</t>
+          <t>Validate Member Details Against State Eligibility</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>User is on enrollment submission page</t>
+          <t>User logged in; Enrollment form open</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1. Enter member details matching an existing record;2. Submit enrollment</t>
+          <t>1. Enter member details that do not match state eligibility;2. Submit enrollment</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>System flags duplicate and prevents submission</t>
+          <t>System flags eligibility validation error; Enrollment not processed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No duplicate member created</t>
+          <t>No member record created</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Enrollment Management</t>
+          <t>Member Enrollment</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Duplicate Detection</t>
+          <t>Eligibility Check</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Edge case: similar names, different DOB</t>
+          <t>Negative scenario for eligibility</t>
         </is>
       </c>
     </row>
@@ -637,32 +637,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enrollment Confirmation Generation</t>
+          <t>Flag Duplicate Member Records</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Successful member enrollment</t>
+          <t>User logged in; Existing member record present</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1. Complete enrollment process;2. Submit details</t>
+          <t>1. Enter member details matching existing record;2. Submit enrollment</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>System generates and displays confirmation</t>
+          <t>System flags duplicate record; Enrollment not processed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Confirmation is stored and accessible</t>
+          <t>No duplicate created</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Enrollment Management</t>
+          <t>Member Enrollment</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Confirmation Generation</t>
+          <t>Duplicate Detection</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Check for confirmation format</t>
+          <t>Negative scenario for duplicates</t>
         </is>
       </c>
     </row>
@@ -704,22 +704,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Claims Validation Against Member Eligibility</t>
+          <t>Adjudicate Valid Medical Claims</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>User is logged into claims system; Member exists</t>
+          <t>User logged in as Claims Processor; Member is eligible</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1. Submit claim for a member;2. System checks eligibility</t>
+          <t>1. Submit medical claim for eligible member;2. System processes claim</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Claim is validated or denied based on eligibility</t>
+          <t>Claim adjudicated successfully; Reimbursement initiated</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Eligibility Validation</t>
+          <t>Adjudication</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Negative: Ineligible member</t>
+          <t>Positive claim processing</t>
         </is>
       </c>
     </row>
@@ -771,32 +771,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Policy Rules and Benefit Limits Application</t>
+          <t>Validate Claim Against Ineligible Member</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Claim is ready for adjudication</t>
+          <t>User logged in; Member is not eligible</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1. Submit claim;2. System applies policy rules;3. System checks benefit limits</t>
+          <t>1. Submit claim for ineligible member</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Claim is adjudicated per rules; limits enforced</t>
+          <t>System rejects claim; Error message displayed</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Claim processed or denied</t>
+          <t>Claim not processed</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Policy Rules</t>
+          <t>Eligibility Validation</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Boundary: Max benefit limit</t>
+          <t>Negative scenario for claim eligibility</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Denied Claims Generate EOB</t>
+          <t>Apply Policy Rules and Benefit Limits</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Claim is denied</t>
+          <t>User logged in; Valid claim submitted</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1. Submit claim with invalid details;2. System denies claim</t>
+          <t>1. Submit claim exceeding benefit limit</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EOB is generated with denial reason</t>
+          <t>System applies benefit limits; Partial or denied payment</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EOB accessible to provider</t>
+          <t>Claim status reflects applied limits</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>EOB Generation</t>
+          <t>Policy Rules</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Check EOB content</t>
+          <t>Boundary scenario for benefit limits</t>
         </is>
       </c>
     </row>
@@ -905,32 +905,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Provider License Validation During Credential Update</t>
+          <t>Generate EOB for Denied Claims</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provider is updating credentials</t>
+          <t>User logged in; Claim denied</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1. Edit provider profile;2. Enter license details;3. Submit update</t>
+          <t>1. View denied claim;2. Check EOB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>System validates license and accepts/rejects update</t>
+          <t>EOB generated with denial reasons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Provider record updated or rejected</t>
+          <t>EOB accessible to provider</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -940,12 +940,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Provider Management</t>
+          <t>Claims Processing</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>License Validation</t>
+          <t>EOB Generation</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Negative: Expired license</t>
+          <t>EOB generation for denials</t>
         </is>
       </c>
     </row>
@@ -972,32 +972,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audit and Log Provider Changes</t>
+          <t>Update Provider Credentialing Information</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provider change is submitted</t>
+          <t>User logged in as Provider Admin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1. Update provider information;2. Submit changes</t>
+          <t>1. Edit provider details;2. Submit changes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>System logs and audits all changes</t>
+          <t>Provider info updated; Changes logged</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Audit log entry created</t>
+          <t>Audit log updated</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Provider Management</t>
+          <t>Provider Network</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Audit Logging</t>
+          <t>Credentialing Update</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Check log for accuracy</t>
+          <t>Basic provider update</t>
         </is>
       </c>
     </row>
@@ -1039,32 +1039,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Provider Info Update Reflected in Portal</t>
+          <t>Validate Provider License</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Provider update is approved</t>
+          <t>User logged in; Provider update initiated</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1. Complete provider update;2. Wait for sync</t>
+          <t>1. Enter invalid license;2. Submit update</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Member portal shows updated provider info within 24 hours</t>
+          <t>System rejects update; License validation error</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Portal data matches backend</t>
+          <t>No update applied</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Provider Management</t>
+          <t>Provider Network</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Portal Sync</t>
+          <t>License Validation</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Check for sync delay</t>
+          <t>Negative license validation</t>
         </is>
       </c>
     </row>
@@ -1106,32 +1106,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Clinical Documentation Required for Prior Auth</t>
+          <t>Reflect Provider Info in Member Portal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nurse is reviewing prior auth request</t>
+          <t>Provider info updated and approved</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1. Open prior auth request;2. Check for attached clinical docs</t>
+          <t>1. Wait 24 hours;2. Check member portal</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>System rejects requests without documentation</t>
+          <t>Updated provider info visible in portal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Request status is updated</t>
+          <t>Portal shows latest data</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Prior Auth Workflow</t>
+          <t>Provider Network</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Documentation Check</t>
+          <t>Portal Sync</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Negative: Missing docs</t>
+          <t>Data propagation scenario</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Case Routing Based on Service Type</t>
+          <t>Review and Approve Prior Auth Request</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prior auth request is submitted</t>
+          <t>User logged in as Care Mgmt Nurse; Request submitted</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1. Submit request with service type;2. System routes case</t>
+          <t>1. Open prior auth request;2. Review docs;3. Approve request</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Case is routed to appropriate queue</t>
+          <t>Request approved; Notification sent</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Queue assignment visible</t>
+          <t>Authorization status updated</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Prior Auth Workflow</t>
+          <t>Prior Auth</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Case Routing</t>
+          <t>Approval Workflow</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Boundary: Unknown type</t>
+          <t>Standard approval path</t>
         </is>
       </c>
     </row>
@@ -1240,32 +1240,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Decision Notifications Sent</t>
+          <t>Reject Prior Auth Missing Documentation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prior auth decision made</t>
+          <t>User logged in; Incomplete request submitted</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1. Approve/deny request;2. System sends notifications</t>
+          <t>1. Attempt to approve request missing docs</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Providers and members receive notifications</t>
+          <t>System rejects approval; Error displayed</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Notification logs updated</t>
+          <t>Request remains pending</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Prior Auth Workflow</t>
+          <t>Prior Auth</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Document Validation</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Check notification content</t>
+          <t>Negative for missing docs</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Secure Login with MFA for Member Portal</t>
+          <t>Route Prior Auth by Service Type</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Member has portal account</t>
+          <t>User logged in; Request submitted</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1. Open portal login;2. Enter credentials;3. Complete MFA</t>
+          <t>1. Submit request for specific service type</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>System authenticates user securely</t>
+          <t>System routes to correct queue/team</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>User gains access</t>
+          <t>Request status updated</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Member Portal</t>
+          <t>Prior Auth</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Routing Logic</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Negative: Wrong MFA code</t>
+          <t>Routing based on service</t>
         </is>
       </c>
     </row>
@@ -1374,32 +1374,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Real-Time Claims Status Visibility</t>
+          <t>Member Portal Secure Login</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Member is logged into portal</t>
+          <t>User is health plan member</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1. Navigate to claims section</t>
+          <t>1. Navigate to portal;2. Enter credentials;3. Complete MFA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Claims status shown in real-time</t>
+          <t>Access granted to portal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Status matches backend</t>
+          <t>User session started</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Claims Status</t>
+          <t>Login &amp; Security</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Check for delays</t>
+          <t>Security scenario MFA</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1441,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Download Digital ID Card</t>
+          <t>View Real-Time Claims Status</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Member is logged into portal</t>
+          <t>User logged in to portal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1. Navigate to ID card section;2. Click download</t>
+          <t>1. Navigate to claims section</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Digital ID card downloads successfully</t>
+          <t>Current claim statuses displayed in real-time</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>File is accessible to member</t>
+          <t>Claims status updated</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ID Card</t>
+          <t>Claims View</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Check file format</t>
+          <t>Claims visibility</t>
         </is>
       </c>
     </row>
@@ -1508,32 +1508,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Regulatory Report Generation per CMS</t>
+          <t>Download Digital ID Card</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>User is compliance officer</t>
+          <t>User logged in; ID card available</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1. Open reporting module;2. Select CMS report;3. Generate report</t>
+          <t>1. Navigate to ID card section;2. Download digital card</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Report matches CMS format</t>
+          <t>Digital ID card downloaded</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Report is stored and accessible</t>
+          <t>File available to user</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Reporting &amp; Compliance</t>
+          <t>Member Portal</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CMS Reporting</t>
+          <t>ID Card</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Check for compliance updates</t>
+          <t>Download functionality</t>
         </is>
       </c>
     </row>
@@ -1575,32 +1575,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Data Extraction from Validated Sources</t>
+          <t>Generate Regulatory Reports</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Reporting job is scheduled</t>
+          <t>User logged in as Compliance Officer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1. Configure data sources;2. Run report job</t>
+          <t>1. Select report type;2. Generate report</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data extracted only from validated sources</t>
+          <t>Report generated per CMS guidelines</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Report accuracy ensured</t>
+          <t>Audit log updated</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Reporting &amp; Compliance</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Data Extraction</t>
+          <t>Compliance Reports</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Negative: Invalid data source</t>
+          <t>Regulatory compliance</t>
         </is>
       </c>
     </row>
@@ -1642,32 +1642,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Audit Logs for Report Generation</t>
+          <t>Validate Data Sources for Reporting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Report is generated</t>
+          <t>User logged in; Report generation started</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1. Generate regulatory report</t>
+          <t>1. Attempt to generate report with unvalidated data</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Audit log entry created for report generation</t>
+          <t>System prevents report generation; Error displayed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Logs are reviewable</t>
+          <t>No report generated</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Centene_Healthcare</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1677,27 +1677,94 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Reporting &amp; Compliance</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>Data Validation</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Negative data validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TS-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Maintain Audit Logs for Reports</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>User logged in; Report generated</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1. Generate report;2. Review audit log</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Audit log entry created for report</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Audit logs updated</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>Audit Logging</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>SIMULATED</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Check for missing logs</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Audit trail validation</t>
         </is>
       </c>
     </row>
